--- a/Scenario Files/HVACScenarios.xlsx
+++ b/Scenario Files/HVACScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6884,6 +6884,126 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>I'm setting the thermostat for bedtime during a spring cold snap. What heat temperature is best for sleeping?</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" t="n">
+        <v>230</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>34</v>
+      </c>
+      <c r="I105" t="n">
+        <v>30</v>
+      </c>
+      <c r="J105" t="n">
+        <v>13</v>
+      </c>
+      <c r="K105" t="n">
+        <v>11</v>
+      </c>
+      <c r="L105" t="n">
+        <v>14</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>sleep</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>64</v>
+      </c>
+      <c r="O105" t="n">
+        <v>67</v>
+      </c>
+      <c r="P105" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>It's a very humid summer night and we're going to sleep. What AC temperature should I use?</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>York, PA</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>240</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>86</v>
+      </c>
+      <c r="I106" t="n">
+        <v>18</v>
+      </c>
+      <c r="J106" t="n">
+        <v>19</v>
+      </c>
+      <c r="K106" t="n">
+        <v>7</v>
+      </c>
+      <c r="L106" t="n">
+        <v>16</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>sleep</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>74</v>
+      </c>
+      <c r="O106" t="n">
+        <v>76</v>
+      </c>
+      <c r="P106" t="n">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Scenario Files/HVACScenarios.xlsx
+++ b/Scenario Files/HVACScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,82 +419,82 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>question</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Square Footage</t>
+          <t>square_footage</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Insulation</t>
+          <t>insulation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Household Size</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Utility Budget</t>
+          <t>utility_budget</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Housing Type</t>
+          <t>housing_type</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Outdoor Temp</t>
+          <t>outdoor_temp</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>House Age</t>
+          <t>house_age</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>R-Value</t>
+          <t>r_value</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>HVAC Age</t>
+          <t>hvac_age</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>seer</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Occupancy context</t>
+          <t>occupancy_context</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Alternative 1</t>
+          <t>alternative_1</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Alternative 2</t>
+          <t>alternative_2</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Alternative 3</t>
+          <t>alternative_3</t>
         </is>
       </c>
     </row>

--- a/Scenario Files/HVACScenarios.xlsx
+++ b/Scenario Files/HVACScenarios.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I'm working from home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm working from home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I'm home all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 2 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what AC temperature should I set?</t>
+          <t>I'm gone most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 1 person — what AC temperature should I set?</t>
+          <t>I'm planning to stay in all day with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I'm around all day with 1 person — what heat temperature should I set?</t>
+          <t>I'm around all day with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what AC temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 2 people — what heat temperature should I set?</t>
+          <t>I'm spending the day at home with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 2 people — what heat temperature should I set?</t>
+          <t>I'm not planning to leave today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1183,7 +1183,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I'm away most of today — what heat temperature should I set?</t>
+          <t>I'm away most of today, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I'm staying home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm staying home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the rowhouse?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,7 +1431,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the rowhouse?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I'm not home today — what AC temperature should I set?</t>
+          <t>I'm not home today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 5 people — what AC temperature should I set?</t>
+          <t>I'm home and not going out with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
+          <t>I'm heading out for a quick errand, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I'm out for a couple hours — what heat temperature should I set for the townhouse?</t>
+          <t>I'm out for a couple hours, what heat temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I'm staying put today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying put today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>I'm working from home today with 4 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2547,7 +2547,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>I'm home all day with 5 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2609,7 +2609,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>I'm running out for a short while — what AC temperature should I set for the townhouse?</t>
+          <t>I'm running out for a short while, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2795,7 +2795,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>I'm gone for a few hours — what AC temperature should I set for the townhouse?</t>
+          <t>I'm gone for a few hours, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2919,7 +2919,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3043,7 +3043,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>I'm out of the house all day — what AC temperature should I set?</t>
+          <t>I'm out of the house all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3105,7 +3105,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the single-family?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3229,7 +3229,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>I'm away for the day — what heat temperature should I set?</t>
+          <t>I'm away for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3415,7 +3415,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3539,7 +3539,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm planning to stay in all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>I'm around all day with 3 people — what AC temperature should I set?</t>
+          <t>I'm around all day with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3787,7 +3787,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
+          <t>I'm heading out and won't be back for hours, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3911,7 +3911,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3973,7 +3973,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>I'm going to be out all day — what AC temperature should I set?</t>
+          <t>I'm going to be out all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4035,7 +4035,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>I'm leaving the house for most of the day — what AC temperature should I set?</t>
+          <t>I'm leaving the house for most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4097,7 +4097,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4221,7 +4221,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>We're about to turn in — what heat temperature should I set overnight?</t>
+          <t>We're about to turn in, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4345,7 +4345,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4407,7 +4407,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
+          <t>I'm spending the day at home with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4469,7 +4469,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 4 people — what AC temperature should I set?</t>
+          <t>I'm not planning to leave today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4779,7 +4779,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>I'm staying home today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying home today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4903,7 +4903,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 4 people — what heat temperature should I set?</t>
+          <t>I'm home and not going out with 4 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4965,7 +4965,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
+          <t>I'm staying put today with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5213,7 +5213,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5399,7 +5399,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>I'm away most of today — what AC temperature should I set?</t>
+          <t>I'm away most of today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5523,7 +5523,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5585,7 +5585,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>I'm home all day with 4 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5647,7 +5647,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5709,7 +5709,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 5 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what heat temperature should I set for the single-family?</t>
+          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5833,7 +5833,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 1 person — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5895,7 +5895,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
+          <t>I'm gone for the entire workday, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5957,7 +5957,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6019,7 +6019,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6143,7 +6143,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>I'm staying in today with 3 people — what heat temperature should I set?</t>
+          <t>I'm staying in today with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6267,7 +6267,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>I'm around all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm around all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6391,7 +6391,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6453,7 +6453,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what heat temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6515,7 +6515,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6639,7 +6639,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6701,7 +6701,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6763,7 +6763,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what heat temperature should I set?</t>
+          <t>I'm gone most of the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6825,7 +6825,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
